--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task019.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task019.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -339,6 +339,50 @@
         <v>5.2599326055393023</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>75</v>
+      </c>
+      <c r="B6" s="0">
+        <v>185</v>
+      </c>
+      <c r="C6" s="0">
+        <v>75</v>
+      </c>
+      <c r="D6" s="0">
+        <v>94.182006401943326</v>
+      </c>
+      <c r="E6" s="0">
+        <v>473.78500000000003</v>
+      </c>
+      <c r="F6" s="0">
+        <v>155.45361751329582</v>
+      </c>
+      <c r="G6" s="0">
+        <v>3377.5179472032778</v>
+      </c>
+      <c r="H6" s="0">
+        <v>-800.85213932780835</v>
+      </c>
+      <c r="I6" s="0">
+        <v>5.2300000000000004</v>
+      </c>
+      <c r="J6" s="0">
+        <v>15.41</v>
+      </c>
+      <c r="K6" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="L6" s="0">
+        <v>3.5699999999999998</v>
+      </c>
+      <c r="M6" s="0">
+        <v>286.20122975094102</v>
+      </c>
+      <c r="N6" s="0">
+        <v>5.2599326055393023</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task019.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task019.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -383,6 +383,94 @@
         <v>5.2599326055393023</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>75</v>
+      </c>
+      <c r="B7" s="0">
+        <v>186</v>
+      </c>
+      <c r="C7" s="0">
+        <v>75</v>
+      </c>
+      <c r="D7" s="0">
+        <v>94.182006401943326</v>
+      </c>
+      <c r="E7" s="0">
+        <v>473.78500000000003</v>
+      </c>
+      <c r="F7" s="0">
+        <v>155.45361751329582</v>
+      </c>
+      <c r="G7" s="0">
+        <v>3377.5179472032778</v>
+      </c>
+      <c r="H7" s="0">
+        <v>-800.85213932780835</v>
+      </c>
+      <c r="I7" s="0">
+        <v>5.2300000000000004</v>
+      </c>
+      <c r="J7" s="0">
+        <v>15.41</v>
+      </c>
+      <c r="K7" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="L7" s="0">
+        <v>3.5699999999999998</v>
+      </c>
+      <c r="M7" s="0">
+        <v>286.20122975094102</v>
+      </c>
+      <c r="N7" s="0">
+        <v>5.2599326055393023</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>75</v>
+      </c>
+      <c r="B8" s="0">
+        <v>187</v>
+      </c>
+      <c r="C8" s="0">
+        <v>75</v>
+      </c>
+      <c r="D8" s="0">
+        <v>94.182006401943326</v>
+      </c>
+      <c r="E8" s="0">
+        <v>473.78500000000003</v>
+      </c>
+      <c r="F8" s="0">
+        <v>155.45361751329582</v>
+      </c>
+      <c r="G8" s="0">
+        <v>3377.5179472032778</v>
+      </c>
+      <c r="H8" s="0">
+        <v>-800.85213932780835</v>
+      </c>
+      <c r="I8" s="0">
+        <v>5.2300000000000004</v>
+      </c>
+      <c r="J8" s="0">
+        <v>15.41</v>
+      </c>
+      <c r="K8" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="L8" s="0">
+        <v>3.5699999999999998</v>
+      </c>
+      <c r="M8" s="0">
+        <v>286.20122975094102</v>
+      </c>
+      <c r="N8" s="0">
+        <v>5.2599326055393023</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>